--- a/98_archivos_curso/calendario_v0.xlsx
+++ b/98_archivos_curso/calendario_v0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgejuvenalcamposferreira/Desktop/Cursos impartidos/TEC/C2 CCM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgejuvenalcamposferreira/Documents/GitHub/TC2002B.651-Ciencia-de-datos/98_archivos_curso/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36F40D08-3094-6145-AE9F-70D4C667B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F321BAB-4245-BB4D-8364-7D3E1BBE9A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23040" yWindow="4000" windowWidth="27640" windowHeight="16940" xr2:uid="{CF4509D0-D1B0-2E41-A87F-9E5422842A17}"/>
+    <workbookView minimized="1" xWindow="23040" yWindow="-5160" windowWidth="27640" windowHeight="16940" xr2:uid="{CF4509D0-D1B0-2E41-A87F-9E5422842A17}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,6 +201,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,6 +262,10 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,6 +603,7 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="67.6640625" customWidth="1"/>
     <col min="3" max="3" width="39.1640625" customWidth="1"/>
     <col min="4" max="4" width="23.83203125" customWidth="1"/>
   </cols>
@@ -626,7 +637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="187" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -640,7 +651,7 @@
         <v>45881</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="323" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -654,7 +665,7 @@
         <v>45888</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="388" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -682,35 +693,35 @@
         <v>45895</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="340" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="6">
         <v>45896</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="6">
         <v>45902</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="404" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -724,7 +735,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="272" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -738,7 +749,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="221" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -752,7 +763,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="356" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -766,7 +777,7 @@
         <v>45923</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="306" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -780,7 +791,7 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="289" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>

--- a/98_archivos_curso/calendario_v0.xlsx
+++ b/98_archivos_curso/calendario_v0.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgejuvenalcamposferreira/Documents/GitHub/TC2002B.651-Ciencia-de-datos/98_archivos_curso/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F321BAB-4245-BB4D-8364-7D3E1BBE9A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D32EF4-77A0-3E4A-A4C3-28183B40A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="23040" yWindow="-5160" windowWidth="27640" windowHeight="16940" xr2:uid="{CF4509D0-D1B0-2E41-A87F-9E5422842A17}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{CF4509D0-D1B0-2E41-A87F-9E5422842A17}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="calendario_planeado" sheetId="1" r:id="rId1"/>
+    <sheet name="calendario_efectivo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>Ciencia de datos para la toma de decisiones</t>
   </si>
@@ -106,62 +107,10 @@
     <t>Continuación a los temas de clústering</t>
   </si>
   <si>
-    <t>Introducción al análisis espacial</t>
-  </si>
-  <si>
-    <t>* Descarga de librerías de procesamiento de datos geográficos
-* Datos espaciales - Archivos
-* Datos espaciales - Sistemas de coordenadas
-* Datos espaciales - Formas geométricas
-* Elaboración de mapas en ggplot</t>
-  </si>
-  <si>
-    <t>Análisis geo-espacial</t>
-  </si>
-  <si>
-    <t>* Elaboración de mapas en leaflet
-* Operaciones con datos geográficos
-* Intersección
-* Unión
-* Obtención de centroide</t>
-  </si>
-  <si>
-    <t>Estadística geo espacial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Estadísticas espaciales
-* Correlación y autocorrelación espaclal
-* Clustering espacial
-</t>
-  </si>
-  <si>
-    <t>Técnicas selectas de manejo de datos espaciales</t>
-  </si>
-  <si>
-    <t>* Polígonos de Thiessen
-* Curvas isócronas
-* Cartogramas
-* Teselaciones hexagonales
-* Rutas óptimas y análisis de redes
-* Kriging
-* Mapas en tres dimensiones</t>
-  </si>
-  <si>
-    <t>Narrativa de comunicación</t>
-  </si>
-  <si>
-    <t>* Visualización de datos - Selección de gráficas
-* Visualización - Diseño 
-* Visualización - Presentación de información 
-* Presentación de información</t>
-  </si>
-  <si>
-    <t>* Ejercicios de integración de modelos y análisis a un informe
-* Diseño de informes y presentaciones
-* Argumentación de decisione en base en evidencia y métricas</t>
-  </si>
-  <si>
     <t>Diseño de calendario en curso</t>
+  </si>
+  <si>
+    <t>Finalización de modelos basados en distancia</t>
   </si>
 </sst>
 </file>
@@ -191,7 +140,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,12 +150,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -262,10 +205,22 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,7 +575,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -697,10 +652,10 @@
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="6">
@@ -711,22 +666,22 @@
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="6">
         <v>45902</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
+      <c r="B11" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>18</v>
@@ -735,75 +690,197 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="6">
         <v>45909</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>22</v>
-      </c>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="6">
         <v>45922</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="119" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="6">
         <v>45923</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="85" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>26</v>
-      </c>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="6">
         <v>45929</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="85" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>27</v>
-      </c>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="6">
         <v>45930</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB179623-B409-3442-88E8-0DE36816DEFB}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="55" style="11" customWidth="1"/>
+    <col min="3" max="3" width="51.83203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="65.83203125" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="119" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="10">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="10">
+        <v>45902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
